--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_战术阵型配置表_Combat_TacticalFormationConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_战术阵型配置表_Combat_TacticalFormationConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,11 +32,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
   <si>
     <t>阵型ID</t>
   </si>
   <si>
+    <t>阵型等级</t>
+  </si>
+  <si>
     <t>阵型名称</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>主键；被 GrantFormationSkill / SkillConfig.FormationId 引用</t>
   </si>
   <si>
+    <t>复合主键之一；≥1；同 Id 用它区分属性</t>
+  </si>
+  <si>
     <t>UI 展示</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t>FormationId</t>
   </si>
   <si>
+    <t>FormationLevel</t>
+  </si>
+  <si>
     <t>DisplayName</t>
   </si>
   <si>
@@ -149,6 +158,18 @@
   </si>
   <si>
     <t>Stat=Strength|Mul=1.15</t>
+  </si>
+  <si>
+    <t>Stat=Strength|Mul=1.2</t>
+  </si>
+  <si>
+    <t>Stat=Strength|Mul=1.25</t>
+  </si>
+  <si>
+    <t>Stat=Strength|Mul=1.30</t>
+  </si>
+  <si>
+    <t>Stat=Strength|Mul=1.35</t>
   </si>
   <si>
     <t>Form_Wedge_02</t>
@@ -786,9 +807,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1135,22 +1159,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="14.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="16.9090909090909" customWidth="1"/>
-    <col min="5" max="5" width="21.0909090909091" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="15.3636363636364" customWidth="1"/>
-    <col min="8" max="8" width="16.1818181818182" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="22.2727272727273" customWidth="1"/>
-    <col min="11" max="11" width="26.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="15.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="14.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="16.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="21.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="15.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="26.7272727272727" customWidth="1"/>
+    <col min="10" max="10" width="26.6363636363636" customWidth="1"/>
+    <col min="11" max="11" width="22.2727272727273" customWidth="1"/>
+    <col min="12" max="12" width="26.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1184,139 +1209,434 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="F4">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="H5" s="2">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8">
         <v>5</v>
       </c>
-      <c r="H4" t="s">
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="I4" t="s">
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
         <v>38</v>
       </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
         <v>42</v>
       </c>
-      <c r="F5">
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
         <v>3</v>
       </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" t="s">
         <v>43</v>
       </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" t="s">
         <v>44</v>
       </c>
-      <c r="K5" t="s">
-        <v>44</v>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_战术阵型配置表_Combat_TacticalFormationConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_战术阵型配置表_Combat_TacticalFormationConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="696"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="61">
   <si>
     <t>阵型ID</t>
   </si>
@@ -151,7 +151,7 @@
     <t>拥有楔阵技能的已上阵士兵可组成楔形编队（标记技能，不驱动战斗）</t>
   </si>
   <si>
-    <t>Skill_Form_Wedge</t>
+    <t>Skill_Form_Wedge_01</t>
   </si>
   <si>
     <t>FormationPattern_Wedge_01</t>
@@ -175,7 +175,7 @@
     <t>Form_Wedge_02</t>
   </si>
   <si>
-    <t>平行阵</t>
+    <t>短平行阵</t>
   </si>
   <si>
     <t>拥有平行阵技能的已上阵士兵可组成两排平行编队（标记技能，不驱动战斗）</t>
@@ -184,10 +184,37 @@
     <t>Skill_Form_Wedge_02</t>
   </si>
   <si>
+    <t>FormationPattern_Wedge_03</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Form_Wedge_03</t>
+  </si>
+  <si>
+    <t>远射平行阵</t>
+  </si>
+  <si>
+    <t>后排可以上射手</t>
+  </si>
+  <si>
+    <t>Skill_Form_Wedge_03</t>
+  </si>
+  <si>
     <t>FormationPattern_Wedge_02</t>
   </si>
   <si>
-    <t/>
+    <t>Form_Wedge_04</t>
+  </si>
+  <si>
+    <t>紧凑平行阵</t>
+  </si>
+  <si>
+    <t>Skill_Form_Wedge_04</t>
+  </si>
+  <si>
+    <t>FormationPattern_Wedge_04</t>
   </si>
 </sst>
 </file>
@@ -807,12 +834,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1159,7 +1187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.1818181818182" customWidth="1"/>
@@ -1293,7 +1321,7 @@
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -1305,14 +1333,14 @@
       <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G4" s="2">
         <v>3</v>
       </c>
       <c r="H4" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>
@@ -1325,7 +1353,7 @@
       <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" t="s">
@@ -1337,14 +1365,12 @@
       <c r="E5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="2">
         <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
@@ -1357,7 +1383,7 @@
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -1369,14 +1395,12 @@
       <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="2">
         <v>3</v>
       </c>
       <c r="H6" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
@@ -1389,7 +1413,7 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
       <c r="C7" t="s">
@@ -1401,14 +1425,12 @@
       <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="2">
         <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -1421,7 +1443,7 @@
       <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
       <c r="C8" t="s">
@@ -1433,14 +1455,12 @@
       <c r="E8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="2">
         <v>3</v>
       </c>
       <c r="H8" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>40</v>
@@ -1453,19 +1473,19 @@
       <c r="A9" t="s">
         <v>46</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G9" s="2">
@@ -1491,21 +1511,19 @@
       <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="2">
         <v>3</v>
       </c>
@@ -1529,21 +1547,19 @@
       <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="2">
         <v>3</v>
       </c>
@@ -1567,21 +1583,19 @@
       <c r="A12" t="s">
         <v>46</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>4</v>
       </c>
       <c r="C12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
       </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="2">
         <v>3</v>
       </c>
@@ -1605,21 +1619,19 @@
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>5</v>
       </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>48</v>
       </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="2">
         <v>3</v>
       </c>
@@ -1637,6 +1649,310 @@
       </c>
       <c r="L13" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="2">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2">
+        <v>12</v>
+      </c>
+      <c r="I14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2">
+        <v>6</v>
+      </c>
+      <c r="H15" s="2">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="2">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2">
+        <v>12</v>
+      </c>
+      <c r="I16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="2">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2">
+        <v>12</v>
+      </c>
+      <c r="I17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="2">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2">
+        <v>12</v>
+      </c>
+      <c r="I18" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2">
+        <v>12</v>
+      </c>
+      <c r="I19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2">
+        <v>12</v>
+      </c>
+      <c r="I20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2">
+        <v>12</v>
+      </c>
+      <c r="I21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="2">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>12</v>
+      </c>
+      <c r="I22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="2">
+        <v>6</v>
+      </c>
+      <c r="H23" s="2">
+        <v>12</v>
+      </c>
+      <c r="I23" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
